--- a/cli/src/test/resources/sample.xlsx
+++ b/cli/src/test/resources/sample.xlsx
@@ -651,8 +651,6 @@
         <v>32</v>
       </c>
       <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
       <c r="K4" s="17"/>
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
@@ -672,8 +670,6 @@
         <v>29</v>
       </c>
       <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="18"/>
       <c r="R5" s="18"/>
     </row>
   </sheetData>
